--- a/AAII_Financials/Yearly/CVNA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CVNA_YR_FIN.xlsx
@@ -1009,10 +1009,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>7000</v>
+        <v>83000</v>
       </c>
       <c r="E14" s="3">
-        <v>1000</v>
+        <v>-91000</v>
       </c>
       <c r="F14" s="3">
         <v>-863000</v>
@@ -1252,10 +1252,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2262000</v>
+        <v>2186000</v>
       </c>
       <c r="E20" s="3">
-        <v>-50000</v>
+        <v>42000</v>
       </c>
       <c r="F20" s="3">
         <v>-9000</v>
@@ -1303,10 +1303,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-214000</v>
+        <v>-138000</v>
       </c>
       <c r="E21" s="3">
-        <v>1217000</v>
+        <v>1125000</v>
       </c>
       <c r="F21" s="3">
         <v>127000</v>
@@ -1864,10 +1864,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2262000</v>
+        <v>-2186000</v>
       </c>
       <c r="E32" s="3">
-        <v>50000</v>
+        <v>-42000</v>
       </c>
       <c r="F32" s="3">
         <v>9000</v>
